--- a/data/H131_20260621_20.xlsx
+++ b/data/H131_20260621_20.xlsx
@@ -237,7 +237,7 @@
         <v>1092.0</v>
       </c>
       <c r="J2" t="n">
-        <v>1022.0</v>
+        <v>1023.0</v>
       </c>
       <c r="K2" t="n">
         <v>1.0</v>
@@ -249,13 +249,13 @@
         <v>0.0</v>
       </c>
       <c r="N2" t="n">
-        <v>1022.0</v>
+        <v>1023.0</v>
       </c>
       <c r="O2" t="n">
         <v>577.0</v>
       </c>
       <c r="P2" t="n">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q2" t="n">
         <v>2.0</v>
@@ -379,7 +379,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" t="n">
-        <v>801.0</v>
+        <v>835.0</v>
       </c>
       <c r="K4" t="n">
         <v>1.0</v>
@@ -391,19 +391,19 @@
         <v>0.0</v>
       </c>
       <c r="N4" t="n">
-        <v>801.0</v>
+        <v>835.0</v>
       </c>
       <c r="O4" t="n">
-        <v>444.0</v>
+        <v>477.0</v>
       </c>
       <c r="P4" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0</v>
       </c>
       <c r="R4" t="n">
-        <v>7.0</v>
+        <v>47.0</v>
       </c>
       <c r="S4" t="n">
         <v>1.0</v>
@@ -418,7 +418,7 @@
         <v>0.0</v>
       </c>
       <c r="W4" t="n">
-        <v>8.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -450,7 +450,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" t="n">
-        <v>629.0</v>
+        <v>630.0</v>
       </c>
       <c r="K5" t="n">
         <v>1.0</v>
@@ -462,13 +462,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" t="n">
-        <v>629.0</v>
+        <v>630.0</v>
       </c>
       <c r="O5" t="n">
         <v>333.0</v>
       </c>
       <c r="P5" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q5" t="n">
         <v>2.0</v>
@@ -521,7 +521,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" t="n">
-        <v>849.0</v>
+        <v>856.0</v>
       </c>
       <c r="K6" t="n">
         <v>1.0</v>
@@ -533,13 +533,13 @@
         <v>0.0</v>
       </c>
       <c r="N6" t="n">
-        <v>849.0</v>
+        <v>856.0</v>
       </c>
       <c r="O6" t="n">
-        <v>456.0</v>
+        <v>461.0</v>
       </c>
       <c r="P6" t="n">
-        <v>393.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0</v>
@@ -734,7 +734,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" t="n">
-        <v>658.0</v>
+        <v>660.0</v>
       </c>
       <c r="K9" t="n">
         <v>1.0</v>
@@ -746,13 +746,13 @@
         <v>0.0</v>
       </c>
       <c r="N9" t="n">
-        <v>658.0</v>
+        <v>660.0</v>
       </c>
       <c r="O9" t="n">
         <v>368.0</v>
       </c>
       <c r="P9" t="n">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0</v>
@@ -974,7 +974,7 @@
         <v>0.0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="T12" t="n">
         <v>0.0</v>
@@ -986,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="W12" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="13">
@@ -1231,7 +1231,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" t="n">
-        <v>581.0</v>
+        <v>582.0</v>
       </c>
       <c r="K16" t="n">
         <v>1.0</v>
@@ -1243,10 +1243,10 @@
         <v>0.0</v>
       </c>
       <c r="N16" t="n">
-        <v>581.0</v>
+        <v>582.0</v>
       </c>
       <c r="O16" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="P16" t="n">
         <v>296.0</v>
@@ -1728,7 +1728,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" t="n">
-        <v>713.0</v>
+        <v>716.0</v>
       </c>
       <c r="K23" t="n">
         <v>1.0</v>
@@ -1740,13 +1740,13 @@
         <v>0.0</v>
       </c>
       <c r="N23" t="n">
-        <v>713.0</v>
+        <v>716.0</v>
       </c>
       <c r="O23" t="n">
         <v>390.0</v>
       </c>
       <c r="P23" t="n">
-        <v>323.0</v>
+        <v>326.0</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0</v>
@@ -1799,7 +1799,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" t="n">
-        <v>1170.0</v>
+        <v>1174.0</v>
       </c>
       <c r="K24" t="n">
         <v>1.0</v>
@@ -1811,10 +1811,10 @@
         <v>0.0</v>
       </c>
       <c r="N24" t="n">
-        <v>1170.0</v>
+        <v>1174.0</v>
       </c>
       <c r="O24" t="n">
-        <v>714.0</v>
+        <v>718.0</v>
       </c>
       <c r="P24" t="n">
         <v>439.0</v>
@@ -1826,7 +1826,7 @@
         <v>22.0</v>
       </c>
       <c r="S24" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T24" t="n">
         <v>3.0</v>
@@ -1838,7 +1838,7 @@
         <v>0.0</v>
       </c>
       <c r="W24" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="25">
@@ -1941,7 +1941,7 @@
         <v>1399.0</v>
       </c>
       <c r="J26" t="n">
-        <v>1288.0</v>
+        <v>1293.0</v>
       </c>
       <c r="K26" t="n">
         <v>1.0</v>
@@ -1953,13 +1953,13 @@
         <v>0.0</v>
       </c>
       <c r="N26" t="n">
-        <v>1288.0</v>
+        <v>1293.0</v>
       </c>
       <c r="O26" t="n">
-        <v>673.0</v>
+        <v>677.0</v>
       </c>
       <c r="P26" t="n">
-        <v>555.0</v>
+        <v>556.0</v>
       </c>
       <c r="Q26" t="n">
         <v>60.0</v>
@@ -2154,7 +2154,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" t="n">
-        <v>850.0</v>
+        <v>868.0</v>
       </c>
       <c r="K29" t="n">
         <v>1.0</v>
@@ -2166,13 +2166,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" t="n">
-        <v>850.0</v>
+        <v>868.0</v>
       </c>
       <c r="O29" t="n">
-        <v>307.0</v>
+        <v>323.0</v>
       </c>
       <c r="P29" t="n">
-        <v>411.0</v>
+        <v>413.0</v>
       </c>
       <c r="Q29" t="n">
         <v>132.0</v>
@@ -2296,7 +2296,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" t="n">
-        <v>1078.0</v>
+        <v>1083.0</v>
       </c>
       <c r="K31" t="n">
         <v>1.0</v>
@@ -2308,13 +2308,13 @@
         <v>0.0</v>
       </c>
       <c r="N31" t="n">
-        <v>1078.0</v>
+        <v>1083.0</v>
       </c>
       <c r="O31" t="n">
-        <v>593.0</v>
+        <v>597.0</v>
       </c>
       <c r="P31" t="n">
-        <v>471.0</v>
+        <v>472.0</v>
       </c>
       <c r="Q31" t="n">
         <v>14.0</v>
@@ -2323,7 +2323,7 @@
         <v>56.0</v>
       </c>
       <c r="S31" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="T31" t="n">
         <v>0.0</v>
@@ -2335,7 +2335,7 @@
         <v>9.0</v>
       </c>
       <c r="W31" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="32">
@@ -2651,7 +2651,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" t="n">
-        <v>901.0</v>
+        <v>915.0</v>
       </c>
       <c r="K36" t="n">
         <v>1.0</v>
@@ -2663,16 +2663,16 @@
         <v>0.0</v>
       </c>
       <c r="N36" t="n">
-        <v>901.0</v>
+        <v>915.0</v>
       </c>
       <c r="O36" t="n">
-        <v>450.0</v>
+        <v>456.0</v>
       </c>
       <c r="P36" t="n">
-        <v>432.0</v>
+        <v>439.0</v>
       </c>
       <c r="Q36" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R36" t="n">
         <v>45.0</v>
@@ -3148,7 +3148,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" t="n">
-        <v>952.0</v>
+        <v>956.0</v>
       </c>
       <c r="K43" t="n">
         <v>1.0</v>
@@ -3160,13 +3160,13 @@
         <v>0.0</v>
       </c>
       <c r="N43" t="n">
-        <v>952.0</v>
+        <v>956.0</v>
       </c>
       <c r="O43" t="n">
-        <v>496.0</v>
+        <v>499.0</v>
       </c>
       <c r="P43" t="n">
-        <v>444.0</v>
+        <v>445.0</v>
       </c>
       <c r="Q43" t="n">
         <v>12.0</v>
@@ -3574,7 +3574,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" t="n">
-        <v>1345.0</v>
+        <v>1354.0</v>
       </c>
       <c r="K49" t="n">
         <v>1.0</v>
@@ -3586,19 +3586,19 @@
         <v>0.0</v>
       </c>
       <c r="N49" t="n">
-        <v>1345.0</v>
+        <v>1354.0</v>
       </c>
       <c r="O49" t="n">
-        <v>773.0</v>
+        <v>777.0</v>
       </c>
       <c r="P49" t="n">
-        <v>533.0</v>
+        <v>538.0</v>
       </c>
       <c r="Q49" t="n">
         <v>39.0</v>
       </c>
       <c r="R49" t="n">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
       <c r="S49" t="n">
         <v>15.0</v>
@@ -3613,7 +3613,7 @@
         <v>0.0</v>
       </c>
       <c r="W49" t="n">
-        <v>79.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="50">
@@ -4639,7 +4639,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" t="n">
-        <v>1085.0</v>
+        <v>1086.0</v>
       </c>
       <c r="K64" t="n">
         <v>1.0</v>
@@ -4651,10 +4651,10 @@
         <v>0.0</v>
       </c>
       <c r="N64" t="n">
-        <v>1085.0</v>
+        <v>1086.0</v>
       </c>
       <c r="O64" t="n">
-        <v>621.0</v>
+        <v>622.0</v>
       </c>
       <c r="P64" t="n">
         <v>464.0</v>
@@ -4710,7 +4710,7 @@
         <v>522.0</v>
       </c>
       <c r="J65" t="n">
-        <v>495.0</v>
+        <v>497.0</v>
       </c>
       <c r="K65" t="n">
         <v>1.0</v>
@@ -4722,13 +4722,13 @@
         <v>0.0</v>
       </c>
       <c r="N65" t="n">
-        <v>495.0</v>
+        <v>497.0</v>
       </c>
       <c r="O65" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="P65" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q65" t="n">
         <v>0.0</v>
@@ -4740,16 +4740,16 @@
         <v>0.0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U65" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V65" t="n">
         <v>0.0</v>
       </c>
       <c r="W65" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="66">
@@ -4799,10 +4799,10 @@
         <v>576.0</v>
       </c>
       <c r="P66" t="n">
-        <v>483.0</v>
+        <v>482.0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R66" t="n">
         <v>27.0</v>
@@ -4852,7 +4852,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" t="n">
-        <v>1044.0</v>
+        <v>1046.0</v>
       </c>
       <c r="K67" t="n">
         <v>1.0</v>
@@ -4864,16 +4864,16 @@
         <v>0.0</v>
       </c>
       <c r="N67" t="n">
-        <v>1044.0</v>
+        <v>1046.0</v>
       </c>
       <c r="O67" t="n">
         <v>500.0</v>
       </c>
       <c r="P67" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="Q67" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="R67" t="n">
         <v>61.0</v>
@@ -5491,7 +5491,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" t="n">
-        <v>888.0</v>
+        <v>891.0</v>
       </c>
       <c r="K76" t="n">
         <v>1.0</v>
@@ -5503,13 +5503,13 @@
         <v>0.0</v>
       </c>
       <c r="N76" t="n">
-        <v>888.0</v>
+        <v>891.0</v>
       </c>
       <c r="O76" t="n">
         <v>487.0</v>
       </c>
       <c r="P76" t="n">
-        <v>401.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q76" t="n">
         <v>0.0</v>
@@ -5518,19 +5518,19 @@
         <v>35.0</v>
       </c>
       <c r="S76" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="T76" t="n">
         <v>8.0</v>
       </c>
       <c r="U76" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="V76" t="n">
         <v>0.0</v>
       </c>
       <c r="W76" t="n">
-        <v>76.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="77">
@@ -5562,7 +5562,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" t="n">
-        <v>657.0</v>
+        <v>662.0</v>
       </c>
       <c r="K77" t="n">
         <v>1.0</v>
@@ -5574,10 +5574,10 @@
         <v>0.0</v>
       </c>
       <c r="N77" t="n">
-        <v>657.0</v>
+        <v>662.0</v>
       </c>
       <c r="O77" t="n">
-        <v>185.0</v>
+        <v>190.0</v>
       </c>
       <c r="P77" t="n">
         <v>315.0</v>
@@ -5633,7 +5633,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" t="n">
-        <v>1013.0</v>
+        <v>1029.0</v>
       </c>
       <c r="K78" t="n">
         <v>1.0</v>
@@ -5645,13 +5645,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" t="n">
-        <v>1013.0</v>
+        <v>1029.0</v>
       </c>
       <c r="O78" t="n">
-        <v>450.0</v>
+        <v>459.0</v>
       </c>
       <c r="P78" t="n">
-        <v>563.0</v>
+        <v>570.0</v>
       </c>
       <c r="Q78" t="n">
         <v>0.0</v>
@@ -5660,19 +5660,19 @@
         <v>51.0</v>
       </c>
       <c r="S78" t="n">
-        <v>42.0</v>
+        <v>54.0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U78" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="V78" t="n">
         <v>0.0</v>
       </c>
       <c r="W78" t="n">
-        <v>94.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="79">
@@ -5775,7 +5775,7 @@
         <v>1333.0</v>
       </c>
       <c r="J80" t="n">
-        <v>1203.0</v>
+        <v>1206.0</v>
       </c>
       <c r="K80" t="n">
         <v>1.0</v>
@@ -5787,13 +5787,13 @@
         <v>0.0</v>
       </c>
       <c r="N80" t="n">
-        <v>1203.0</v>
+        <v>1206.0</v>
       </c>
       <c r="O80" t="n">
-        <v>650.0</v>
+        <v>652.0</v>
       </c>
       <c r="P80" t="n">
-        <v>546.0</v>
+        <v>547.0</v>
       </c>
       <c r="Q80" t="n">
         <v>7.0</v>
@@ -5917,7 +5917,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" t="n">
-        <v>963.0</v>
+        <v>975.0</v>
       </c>
       <c r="K82" t="n">
         <v>1.0</v>
@@ -5929,13 +5929,13 @@
         <v>0.0</v>
       </c>
       <c r="N82" t="n">
-        <v>963.0</v>
+        <v>975.0</v>
       </c>
       <c r="O82" t="n">
-        <v>489.0</v>
+        <v>500.0</v>
       </c>
       <c r="P82" t="n">
-        <v>474.0</v>
+        <v>475.0</v>
       </c>
       <c r="Q82" t="n">
         <v>0.0</v>
@@ -6627,7 +6627,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" t="n">
-        <v>1033.0</v>
+        <v>1046.0</v>
       </c>
       <c r="K92" t="n">
         <v>1.0</v>
@@ -6639,34 +6639,34 @@
         <v>0.0</v>
       </c>
       <c r="N92" t="n">
-        <v>1033.0</v>
+        <v>1046.0</v>
       </c>
       <c r="O92" t="n">
-        <v>538.0</v>
+        <v>547.0</v>
       </c>
       <c r="P92" t="n">
-        <v>385.0</v>
+        <v>386.0</v>
       </c>
       <c r="Q92" t="n">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
       <c r="R92" t="n">
         <v>59.0</v>
       </c>
       <c r="S92" t="n">
-        <v>118.0</v>
+        <v>122.0</v>
       </c>
       <c r="T92" t="n">
         <v>19.0</v>
       </c>
       <c r="U92" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="V92" t="n">
         <v>2.0</v>
       </c>
       <c r="W92" t="n">
-        <v>201.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="93">
@@ -6867,7 +6867,7 @@
         <v>1.0</v>
       </c>
       <c r="S95" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T95" t="n">
         <v>0.0</v>
@@ -6879,7 +6879,7 @@
         <v>0.0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="96">
@@ -6911,7 +6911,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" t="n">
-        <v>1302.0</v>
+        <v>1309.0</v>
       </c>
       <c r="K96" t="n">
         <v>1.0</v>
@@ -6923,19 +6923,19 @@
         <v>0.0</v>
       </c>
       <c r="N96" t="n">
-        <v>1302.0</v>
+        <v>1309.0</v>
       </c>
       <c r="O96" t="n">
-        <v>780.0</v>
+        <v>783.0</v>
       </c>
       <c r="P96" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
       <c r="Q96" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="R96" t="n">
-        <v>29.0</v>
+        <v>45.0</v>
       </c>
       <c r="S96" t="n">
         <v>29.0</v>
@@ -6950,7 +6950,7 @@
         <v>0.0</v>
       </c>
       <c r="W96" t="n">
-        <v>58.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="97">
@@ -7053,7 +7053,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" t="n">
-        <v>1354.0</v>
+        <v>1356.0</v>
       </c>
       <c r="K98" t="n">
         <v>1.0</v>
@@ -7065,22 +7065,22 @@
         <v>0.0</v>
       </c>
       <c r="N98" t="n">
-        <v>1354.0</v>
+        <v>1356.0</v>
       </c>
       <c r="O98" t="n">
         <v>724.0</v>
       </c>
       <c r="P98" t="n">
-        <v>620.0</v>
+        <v>622.0</v>
       </c>
       <c r="Q98" t="n">
         <v>10.0</v>
       </c>
       <c r="R98" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="S98" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="T98" t="n">
         <v>4.0</v>
@@ -7092,7 +7092,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="99">
@@ -7905,7 +7905,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" t="n">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="K110" t="n">
         <v>1.0</v>
@@ -7917,7 +7917,7 @@
         <v>0.0</v>
       </c>
       <c r="N110" t="n">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="O110" t="n">
         <v>329.0</v>
@@ -7926,7 +7926,7 @@
         <v>307.0</v>
       </c>
       <c r="Q110" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R110" t="n">
         <v>48.0</v>
@@ -8189,7 +8189,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" t="n">
-        <v>831.0</v>
+        <v>832.0</v>
       </c>
       <c r="K114" t="n">
         <v>1.0</v>
@@ -8201,10 +8201,10 @@
         <v>0.0</v>
       </c>
       <c r="N114" t="n">
-        <v>831.0</v>
+        <v>832.0</v>
       </c>
       <c r="O114" t="n">
-        <v>500.0</v>
+        <v>501.0</v>
       </c>
       <c r="P114" t="n">
         <v>330.0</v>
@@ -8213,7 +8213,7 @@
         <v>1.0</v>
       </c>
       <c r="R114" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="S114" t="n">
         <v>4.0</v>
@@ -8228,7 +8228,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="115">
@@ -8287,7 +8287,7 @@
         <v>41.0</v>
       </c>
       <c r="S115" t="n">
-        <v>34.0</v>
+        <v>42.0</v>
       </c>
       <c r="T115" t="n">
         <v>1.0</v>
@@ -8299,7 +8299,7 @@
         <v>0.0</v>
       </c>
       <c r="W115" t="n">
-        <v>157.0</v>
+        <v>165.0</v>
       </c>
     </row>
     <row r="116">
@@ -8402,22 +8402,22 @@
         <v>1078.0</v>
       </c>
       <c r="J117" t="n">
+        <v>796.0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N117" t="n">
         <v>795.0</v>
       </c>
-      <c r="K117" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>794.0</v>
-      </c>
       <c r="O117" t="n">
-        <v>388.0</v>
+        <v>389.0</v>
       </c>
       <c r="P117" t="n">
         <v>389.0</v>
@@ -8429,7 +8429,7 @@
         <v>25.0</v>
       </c>
       <c r="S117" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="T117" t="n">
         <v>0.0</v>
@@ -8441,7 +8441,7 @@
         <v>0.0</v>
       </c>
       <c r="W117" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="118">
@@ -8473,7 +8473,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" t="n">
-        <v>987.0</v>
+        <v>1000.0</v>
       </c>
       <c r="K118" t="n">
         <v>1.0</v>
@@ -8485,13 +8485,13 @@
         <v>0.0</v>
       </c>
       <c r="N118" t="n">
-        <v>987.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O118" t="n">
-        <v>545.0</v>
+        <v>556.0</v>
       </c>
       <c r="P118" t="n">
-        <v>437.0</v>
+        <v>439.0</v>
       </c>
       <c r="Q118" t="n">
         <v>5.0</v>
@@ -8615,7 +8615,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" t="n">
-        <v>780.0</v>
+        <v>783.0</v>
       </c>
       <c r="K120" t="n">
         <v>1.0</v>
@@ -8627,13 +8627,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" t="n">
-        <v>780.0</v>
+        <v>783.0</v>
       </c>
       <c r="O120" t="n">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
       <c r="P120" t="n">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q120" t="n">
         <v>5.0</v>
@@ -8686,7 +8686,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" t="n">
-        <v>1083.0</v>
+        <v>1103.0</v>
       </c>
       <c r="K121" t="n">
         <v>1.0</v>
@@ -8698,16 +8698,16 @@
         <v>0.0</v>
       </c>
       <c r="N121" t="n">
-        <v>1083.0</v>
+        <v>1103.0</v>
       </c>
       <c r="O121" t="n">
-        <v>702.0</v>
+        <v>708.0</v>
       </c>
       <c r="P121" t="n">
-        <v>380.0</v>
+        <v>390.0</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="R121" t="n">
         <v>25.0</v>
@@ -8757,7 +8757,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" t="n">
-        <v>714.0</v>
+        <v>719.0</v>
       </c>
       <c r="K122" t="n">
         <v>1.0</v>
@@ -8769,19 +8769,19 @@
         <v>4.0</v>
       </c>
       <c r="N122" t="n">
-        <v>710.0</v>
+        <v>715.0</v>
       </c>
       <c r="O122" t="n">
-        <v>397.0</v>
+        <v>401.0</v>
       </c>
       <c r="P122" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q122" t="n">
         <v>15.0</v>
       </c>
       <c r="R122" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="S122" t="n">
         <v>16.0</v>
@@ -8796,7 +8796,7 @@
         <v>1.0</v>
       </c>
       <c r="W122" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="123">
@@ -9287,13 +9287,13 @@
         <v>6.0</v>
       </c>
       <c r="U129" t="n">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="V129" t="n">
         <v>7.0</v>
       </c>
       <c r="W129" t="n">
-        <v>245.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="130">
@@ -9467,7 +9467,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" t="n">
-        <v>1343.0</v>
+        <v>1354.0</v>
       </c>
       <c r="K132" t="n">
         <v>1.0</v>
@@ -9479,19 +9479,19 @@
         <v>0.0</v>
       </c>
       <c r="N132" t="n">
-        <v>1343.0</v>
+        <v>1354.0</v>
       </c>
       <c r="O132" t="n">
-        <v>759.0</v>
+        <v>767.0</v>
       </c>
       <c r="P132" t="n">
-        <v>560.0</v>
+        <v>563.0</v>
       </c>
       <c r="Q132" t="n">
         <v>24.0</v>
       </c>
       <c r="R132" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="S132" t="n">
         <v>3.0</v>
@@ -9500,13 +9500,13 @@
         <v>13.0</v>
       </c>
       <c r="U132" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="V132" t="n">
         <v>0.0</v>
       </c>
       <c r="W132" t="n">
-        <v>61.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="133">
@@ -9538,7 +9538,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" t="n">
-        <v>1213.0</v>
+        <v>1219.0</v>
       </c>
       <c r="K133" t="n">
         <v>1.0</v>
@@ -9550,10 +9550,10 @@
         <v>0.0</v>
       </c>
       <c r="N133" t="n">
-        <v>1213.0</v>
+        <v>1219.0</v>
       </c>
       <c r="O133" t="n">
-        <v>637.0</v>
+        <v>643.0</v>
       </c>
       <c r="P133" t="n">
         <v>536.0</v>
@@ -9751,7 +9751,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" t="n">
-        <v>997.0</v>
+        <v>1006.0</v>
       </c>
       <c r="K136" t="n">
         <v>1.0</v>
@@ -9763,16 +9763,16 @@
         <v>0.0</v>
       </c>
       <c r="N136" t="n">
-        <v>997.0</v>
+        <v>1006.0</v>
       </c>
       <c r="O136" t="n">
-        <v>513.0</v>
+        <v>516.0</v>
       </c>
       <c r="P136" t="n">
-        <v>448.0</v>
+        <v>452.0</v>
       </c>
       <c r="Q136" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="R136" t="n">
         <v>36.0</v>
@@ -9964,7 +9964,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" t="n">
-        <v>1063.0</v>
+        <v>1087.0</v>
       </c>
       <c r="K139" t="n">
         <v>1.0</v>
@@ -9976,13 +9976,13 @@
         <v>0.0</v>
       </c>
       <c r="N139" t="n">
-        <v>1063.0</v>
+        <v>1087.0</v>
       </c>
       <c r="O139" t="n">
-        <v>654.0</v>
+        <v>672.0</v>
       </c>
       <c r="P139" t="n">
-        <v>386.0</v>
+        <v>392.0</v>
       </c>
       <c r="Q139" t="n">
         <v>23.0</v>
@@ -9991,7 +9991,7 @@
         <v>31.0</v>
       </c>
       <c r="S139" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="T139" t="n">
         <v>0.0</v>
@@ -10003,7 +10003,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="140">
@@ -10035,7 +10035,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" t="n">
-        <v>923.0</v>
+        <v>936.0</v>
       </c>
       <c r="K140" t="n">
         <v>1.0</v>
@@ -10047,13 +10047,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" t="n">
-        <v>923.0</v>
+        <v>936.0</v>
       </c>
       <c r="O140" t="n">
-        <v>488.0</v>
+        <v>497.0</v>
       </c>
       <c r="P140" t="n">
-        <v>428.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q140" t="n">
         <v>7.0</v>
@@ -10106,7 +10106,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" t="n">
-        <v>1039.0</v>
+        <v>1057.0</v>
       </c>
       <c r="K141" t="n">
         <v>1.0</v>
@@ -10118,16 +10118,16 @@
         <v>1.0</v>
       </c>
       <c r="N141" t="n">
-        <v>1038.0</v>
+        <v>1056.0</v>
       </c>
       <c r="O141" t="n">
-        <v>647.0</v>
+        <v>658.0</v>
       </c>
       <c r="P141" t="n">
-        <v>382.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q141" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="R141" t="n">
         <v>24.0</v>
@@ -10248,7 +10248,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" t="n">
-        <v>969.0</v>
+        <v>1004.0</v>
       </c>
       <c r="K143" t="n">
         <v>1.0</v>
@@ -10260,13 +10260,13 @@
         <v>1.0</v>
       </c>
       <c r="N143" t="n">
-        <v>968.0</v>
+        <v>1003.0</v>
       </c>
       <c r="O143" t="n">
-        <v>576.0</v>
+        <v>585.0</v>
       </c>
       <c r="P143" t="n">
-        <v>392.0</v>
+        <v>418.0</v>
       </c>
       <c r="Q143" t="n">
         <v>1.0</v>
@@ -10319,7 +10319,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" t="n">
-        <v>1126.0</v>
+        <v>1146.0</v>
       </c>
       <c r="K144" t="n">
         <v>1.0</v>
@@ -10331,13 +10331,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" t="n">
-        <v>1126.0</v>
+        <v>1146.0</v>
       </c>
       <c r="O144" t="n">
-        <v>635.0</v>
+        <v>643.0</v>
       </c>
       <c r="P144" t="n">
-        <v>491.0</v>
+        <v>503.0</v>
       </c>
       <c r="Q144" t="n">
         <v>0.0</v>
@@ -10390,7 +10390,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" t="n">
-        <v>913.0</v>
+        <v>927.0</v>
       </c>
       <c r="K145" t="n">
         <v>1.0</v>
@@ -10402,16 +10402,16 @@
         <v>0.0</v>
       </c>
       <c r="N145" t="n">
-        <v>913.0</v>
+        <v>927.0</v>
       </c>
       <c r="O145" t="n">
-        <v>408.0</v>
+        <v>411.0</v>
       </c>
       <c r="P145" t="n">
-        <v>469.0</v>
+        <v>478.0</v>
       </c>
       <c r="Q145" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="R145" t="n">
         <v>18.0</v>
@@ -10420,16 +10420,16 @@
         <v>22.0</v>
       </c>
       <c r="T145" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="U145" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="V145" t="n">
         <v>1.0</v>
       </c>
       <c r="W145" t="n">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="146">
@@ -10674,7 +10674,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" t="n">
-        <v>700.0</v>
+        <v>711.0</v>
       </c>
       <c r="K149" t="n">
         <v>1.0</v>
@@ -10686,13 +10686,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" t="n">
-        <v>700.0</v>
+        <v>711.0</v>
       </c>
       <c r="O149" t="n">
-        <v>417.0</v>
+        <v>422.0</v>
       </c>
       <c r="P149" t="n">
-        <v>278.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q149" t="n">
         <v>5.0</v>
@@ -10887,7 +10887,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" t="n">
-        <v>745.0</v>
+        <v>763.0</v>
       </c>
       <c r="K152" t="n">
         <v>1.0</v>
@@ -10899,13 +10899,13 @@
         <v>1.0</v>
       </c>
       <c r="N152" t="n">
-        <v>744.0</v>
+        <v>762.0</v>
       </c>
       <c r="O152" t="n">
-        <v>373.0</v>
+        <v>381.0</v>
       </c>
       <c r="P152" t="n">
-        <v>372.0</v>
+        <v>382.0</v>
       </c>
       <c r="Q152" t="n">
         <v>0.0</v>
@@ -10958,7 +10958,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" t="n">
-        <v>846.0</v>
+        <v>853.0</v>
       </c>
       <c r="K153" t="n">
         <v>1.0</v>
@@ -10970,13 +10970,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" t="n">
-        <v>846.0</v>
+        <v>853.0</v>
       </c>
       <c r="O153" t="n">
-        <v>412.0</v>
+        <v>414.0</v>
       </c>
       <c r="P153" t="n">
-        <v>433.0</v>
+        <v>438.0</v>
       </c>
       <c r="Q153" t="n">
         <v>1.0</v>
@@ -11029,7 +11029,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" t="n">
-        <v>740.0</v>
+        <v>766.0</v>
       </c>
       <c r="K154" t="n">
         <v>1.0</v>
@@ -11041,13 +11041,13 @@
         <v>0.0</v>
       </c>
       <c r="N154" t="n">
-        <v>740.0</v>
+        <v>766.0</v>
       </c>
       <c r="O154" t="n">
-        <v>162.0</v>
+        <v>184.0</v>
       </c>
       <c r="P154" t="n">
-        <v>345.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q154" t="n">
         <v>233.0</v>
@@ -11100,7 +11100,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" t="n">
-        <v>1069.0</v>
+        <v>1102.0</v>
       </c>
       <c r="K155" t="n">
         <v>1.0</v>
@@ -11112,13 +11112,13 @@
         <v>0.0</v>
       </c>
       <c r="N155" t="n">
-        <v>1069.0</v>
+        <v>1102.0</v>
       </c>
       <c r="O155" t="n">
-        <v>544.0</v>
+        <v>575.0</v>
       </c>
       <c r="P155" t="n">
-        <v>524.0</v>
+        <v>526.0</v>
       </c>
       <c r="Q155" t="n">
         <v>1.0</v>
@@ -11384,7 +11384,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" t="n">
-        <v>996.0</v>
+        <v>1004.0</v>
       </c>
       <c r="K159" t="n">
         <v>1.0</v>
@@ -11396,10 +11396,10 @@
         <v>1.0</v>
       </c>
       <c r="N159" t="n">
-        <v>995.0</v>
+        <v>1003.0</v>
       </c>
       <c r="O159" t="n">
-        <v>584.0</v>
+        <v>592.0</v>
       </c>
       <c r="P159" t="n">
         <v>412.0</v>
@@ -11411,7 +11411,7 @@
         <v>30.0</v>
       </c>
       <c r="S159" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="T159" t="n">
         <v>0.0</v>
@@ -11423,7 +11423,7 @@
         <v>0.0</v>
       </c>
       <c r="W159" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="160">
@@ -11455,7 +11455,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" t="n">
-        <v>1154.0</v>
+        <v>1158.0</v>
       </c>
       <c r="K160" t="n">
         <v>1.0</v>
@@ -11467,13 +11467,13 @@
         <v>0.0</v>
       </c>
       <c r="N160" t="n">
-        <v>1154.0</v>
+        <v>1158.0</v>
       </c>
       <c r="O160" t="n">
-        <v>594.0</v>
+        <v>596.0</v>
       </c>
       <c r="P160" t="n">
-        <v>560.0</v>
+        <v>562.0</v>
       </c>
       <c r="Q160" t="n">
         <v>0.0</v>
@@ -11526,7 +11526,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" t="n">
-        <v>1037.0</v>
+        <v>1039.0</v>
       </c>
       <c r="K161" t="n">
         <v>1.0</v>
@@ -11538,13 +11538,13 @@
         <v>0.0</v>
       </c>
       <c r="N161" t="n">
-        <v>1037.0</v>
+        <v>1039.0</v>
       </c>
       <c r="O161" t="n">
-        <v>556.0</v>
+        <v>557.0</v>
       </c>
       <c r="P161" t="n">
-        <v>473.0</v>
+        <v>474.0</v>
       </c>
       <c r="Q161" t="n">
         <v>8.0</v>
@@ -11597,7 +11597,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" t="n">
-        <v>979.0</v>
+        <v>986.0</v>
       </c>
       <c r="K162" t="n">
         <v>1.0</v>
@@ -11609,19 +11609,19 @@
         <v>1.0</v>
       </c>
       <c r="N162" t="n">
-        <v>978.0</v>
+        <v>985.0</v>
       </c>
       <c r="O162" t="n">
-        <v>57.0</v>
+        <v>60.0</v>
       </c>
       <c r="P162" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
       <c r="Q162" t="n">
-        <v>712.0</v>
+        <v>714.0</v>
       </c>
       <c r="R162" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="S162" t="n">
         <v>0.0</v>
@@ -11636,7 +11636,7 @@
         <v>1.0</v>
       </c>
       <c r="W162" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="163">
@@ -11739,7 +11739,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" t="n">
-        <v>860.0</v>
+        <v>868.0</v>
       </c>
       <c r="K164" t="n">
         <v>1.0</v>
@@ -11751,13 +11751,13 @@
         <v>1.0</v>
       </c>
       <c r="N164" t="n">
-        <v>859.0</v>
+        <v>867.0</v>
       </c>
       <c r="O164" t="n">
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="P164" t="n">
-        <v>396.0</v>
+        <v>401.0</v>
       </c>
       <c r="Q164" t="n">
         <v>409.0</v>
@@ -11881,7 +11881,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" t="n">
-        <v>789.0</v>
+        <v>794.0</v>
       </c>
       <c r="K166" t="n">
         <v>1.0</v>
@@ -11893,13 +11893,13 @@
         <v>0.0</v>
       </c>
       <c r="N166" t="n">
-        <v>789.0</v>
+        <v>794.0</v>
       </c>
       <c r="O166" t="n">
-        <v>446.0</v>
+        <v>449.0</v>
       </c>
       <c r="P166" t="n">
-        <v>343.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q166" t="n">
         <v>0.0</v>
@@ -12378,7 +12378,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" t="n">
-        <v>1101.0</v>
+        <v>1118.0</v>
       </c>
       <c r="K173" t="n">
         <v>1.0</v>
@@ -12390,13 +12390,13 @@
         <v>0.0</v>
       </c>
       <c r="N173" t="n">
-        <v>1101.0</v>
+        <v>1118.0</v>
       </c>
       <c r="O173" t="n">
-        <v>617.0</v>
+        <v>632.0</v>
       </c>
       <c r="P173" t="n">
-        <v>484.0</v>
+        <v>486.0</v>
       </c>
       <c r="Q173" t="n">
         <v>0.0</v>
@@ -12591,7 +12591,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" t="n">
-        <v>717.0</v>
+        <v>719.0</v>
       </c>
       <c r="K176" t="n">
         <v>1.0</v>
@@ -12603,19 +12603,19 @@
         <v>0.0</v>
       </c>
       <c r="N176" t="n">
-        <v>717.0</v>
+        <v>719.0</v>
       </c>
       <c r="O176" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="P176" t="n">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="Q176" t="n">
         <v>2.0</v>
       </c>
       <c r="R176" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="S176" t="n">
         <v>22.0</v>
@@ -12630,7 +12630,7 @@
         <v>2.0</v>
       </c>
       <c r="W176" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="177">
@@ -12662,7 +12662,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" t="n">
-        <v>680.0</v>
+        <v>698.0</v>
       </c>
       <c r="K177" t="n">
         <v>1.0</v>
@@ -12674,13 +12674,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" t="n">
-        <v>680.0</v>
+        <v>698.0</v>
       </c>
       <c r="O177" t="n">
-        <v>393.0</v>
+        <v>402.0</v>
       </c>
       <c r="P177" t="n">
-        <v>287.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q177" t="n">
         <v>0.0</v>
@@ -12695,13 +12695,13 @@
         <v>4.0</v>
       </c>
       <c r="U177" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="V177" t="n">
         <v>0.0</v>
       </c>
       <c r="W177" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="178">
@@ -12733,7 +12733,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" t="n">
-        <v>655.0</v>
+        <v>663.0</v>
       </c>
       <c r="K178" t="n">
         <v>1.0</v>
@@ -12745,13 +12745,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" t="n">
-        <v>655.0</v>
+        <v>663.0</v>
       </c>
       <c r="O178" t="n">
-        <v>326.0</v>
+        <v>330.0</v>
       </c>
       <c r="P178" t="n">
-        <v>328.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q178" t="n">
         <v>1.0</v>
@@ -12760,19 +12760,19 @@
         <v>18.0</v>
       </c>
       <c r="S178" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T178" t="n">
         <v>2.0</v>
       </c>
       <c r="U178" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="V178" t="n">
         <v>0.0</v>
       </c>
       <c r="W178" t="n">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="179">
@@ -12804,7 +12804,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" t="n">
-        <v>862.0</v>
+        <v>876.0</v>
       </c>
       <c r="K179" t="n">
         <v>1.0</v>
@@ -12816,13 +12816,13 @@
         <v>0.0</v>
       </c>
       <c r="N179" t="n">
-        <v>862.0</v>
+        <v>876.0</v>
       </c>
       <c r="O179" t="n">
-        <v>531.0</v>
+        <v>541.0</v>
       </c>
       <c r="P179" t="n">
-        <v>330.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q179" t="n">
         <v>1.0</v>
@@ -12875,7 +12875,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" t="n">
-        <v>551.0</v>
+        <v>560.0</v>
       </c>
       <c r="K180" t="n">
         <v>1.0</v>
@@ -12887,25 +12887,25 @@
         <v>0.0</v>
       </c>
       <c r="N180" t="n">
-        <v>551.0</v>
+        <v>560.0</v>
       </c>
       <c r="O180" t="n">
-        <v>283.0</v>
+        <v>289.0</v>
       </c>
       <c r="P180" t="n">
-        <v>268.0</v>
+        <v>271.0</v>
       </c>
       <c r="Q180" t="n">
         <v>0.0</v>
       </c>
       <c r="R180" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="S180" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="T180" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="U180" t="n">
         <v>2.0</v>
@@ -12914,7 +12914,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" t="n">
-        <v>45.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="181">
@@ -13230,7 +13230,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" t="n">
-        <v>903.0</v>
+        <v>912.0</v>
       </c>
       <c r="K185" t="n">
         <v>1.0</v>
@@ -13242,13 +13242,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" t="n">
-        <v>903.0</v>
+        <v>912.0</v>
       </c>
       <c r="O185" t="n">
-        <v>486.0</v>
+        <v>491.0</v>
       </c>
       <c r="P185" t="n">
-        <v>417.0</v>
+        <v>421.0</v>
       </c>
       <c r="Q185" t="n">
         <v>0.0</v>
@@ -13301,7 +13301,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" t="n">
-        <v>953.0</v>
+        <v>956.0</v>
       </c>
       <c r="K186" t="n">
         <v>1.0</v>
@@ -13313,10 +13313,10 @@
         <v>0.0</v>
       </c>
       <c r="N186" t="n">
-        <v>953.0</v>
+        <v>956.0</v>
       </c>
       <c r="O186" t="n">
-        <v>296.0</v>
+        <v>299.0</v>
       </c>
       <c r="P186" t="n">
         <v>395.0</v>
@@ -13585,7 +13585,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" t="n">
-        <v>1212.0</v>
+        <v>1232.0</v>
       </c>
       <c r="K190" t="n">
         <v>1.0</v>
@@ -13597,13 +13597,13 @@
         <v>0.0</v>
       </c>
       <c r="N190" t="n">
-        <v>1212.0</v>
+        <v>1232.0</v>
       </c>
       <c r="O190" t="n">
-        <v>712.0</v>
+        <v>726.0</v>
       </c>
       <c r="P190" t="n">
-        <v>468.0</v>
+        <v>474.0</v>
       </c>
       <c r="Q190" t="n">
         <v>32.0</v>
@@ -13798,7 +13798,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" t="n">
-        <v>1180.0</v>
+        <v>1189.0</v>
       </c>
       <c r="K193" t="n">
         <v>1.0</v>
@@ -13810,13 +13810,13 @@
         <v>0.0</v>
       </c>
       <c r="N193" t="n">
-        <v>1180.0</v>
+        <v>1189.0</v>
       </c>
       <c r="O193" t="n">
-        <v>442.0</v>
+        <v>447.0</v>
       </c>
       <c r="P193" t="n">
-        <v>520.0</v>
+        <v>524.0</v>
       </c>
       <c r="Q193" t="n">
         <v>218.0</v>
@@ -13869,7 +13869,7 @@
         <v>452.0</v>
       </c>
       <c r="J194" t="n">
-        <v>390.0</v>
+        <v>391.0</v>
       </c>
       <c r="K194" t="n">
         <v>1.0</v>
@@ -13881,10 +13881,10 @@
         <v>0.0</v>
       </c>
       <c r="N194" t="n">
-        <v>390.0</v>
+        <v>391.0</v>
       </c>
       <c r="O194" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="P194" t="n">
         <v>229.0</v>
@@ -14183,7 +14183,7 @@
         <v>121.0</v>
       </c>
       <c r="T198" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="U198" t="n">
         <v>0.0</v>
@@ -14192,7 +14192,7 @@
         <v>0.0</v>
       </c>
       <c r="W198" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="199">
@@ -14295,7 +14295,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" t="n">
-        <v>604.0</v>
+        <v>606.0</v>
       </c>
       <c r="K200" t="n">
         <v>1.0</v>
@@ -14307,13 +14307,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" t="n">
-        <v>604.0</v>
+        <v>606.0</v>
       </c>
       <c r="O200" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="P200" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="Q200" t="n">
         <v>3.0</v>
@@ -14366,7 +14366,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" t="n">
-        <v>1174.0</v>
+        <v>1175.0</v>
       </c>
       <c r="K201" t="n">
         <v>1.0</v>
@@ -14378,13 +14378,13 @@
         <v>0.0</v>
       </c>
       <c r="N201" t="n">
-        <v>1174.0</v>
+        <v>1175.0</v>
       </c>
       <c r="O201" t="n">
         <v>624.0</v>
       </c>
       <c r="P201" t="n">
-        <v>538.0</v>
+        <v>539.0</v>
       </c>
       <c r="Q201" t="n">
         <v>12.0</v>
@@ -14437,7 +14437,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" t="n">
-        <v>997.0</v>
+        <v>1007.0</v>
       </c>
       <c r="K202" t="n">
         <v>1.0</v>
@@ -14449,13 +14449,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" t="n">
-        <v>997.0</v>
+        <v>1007.0</v>
       </c>
       <c r="O202" t="n">
-        <v>606.0</v>
+        <v>610.0</v>
       </c>
       <c r="P202" t="n">
-        <v>391.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q202" t="n">
         <v>0.0</v>
@@ -14508,7 +14508,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" t="n">
-        <v>859.0</v>
+        <v>860.0</v>
       </c>
       <c r="K203" t="n">
         <v>1.0</v>
@@ -14520,10 +14520,10 @@
         <v>0.0</v>
       </c>
       <c r="N203" t="n">
-        <v>859.0</v>
+        <v>860.0</v>
       </c>
       <c r="O203" t="n">
-        <v>505.0</v>
+        <v>506.0</v>
       </c>
       <c r="P203" t="n">
         <v>353.0</v>
@@ -14579,7 +14579,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" t="n">
-        <v>931.0</v>
+        <v>956.0</v>
       </c>
       <c r="K204" t="n">
         <v>1.0</v>
@@ -14591,13 +14591,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" t="n">
-        <v>931.0</v>
+        <v>956.0</v>
       </c>
       <c r="O204" t="n">
-        <v>493.0</v>
+        <v>507.0</v>
       </c>
       <c r="P204" t="n">
-        <v>421.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q204" t="n">
         <v>17.0</v>
@@ -14612,13 +14612,13 @@
         <v>0.0</v>
       </c>
       <c r="U204" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="V204" t="n">
         <v>0.0</v>
       </c>
       <c r="W204" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="205">
@@ -14650,7 +14650,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" t="n">
-        <v>704.0</v>
+        <v>730.0</v>
       </c>
       <c r="K205" t="n">
         <v>1.0</v>
@@ -14662,13 +14662,13 @@
         <v>0.0</v>
       </c>
       <c r="N205" t="n">
-        <v>704.0</v>
+        <v>730.0</v>
       </c>
       <c r="O205" t="n">
-        <v>370.0</v>
+        <v>388.0</v>
       </c>
       <c r="P205" t="n">
-        <v>287.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q205" t="n">
         <v>47.0</v>
@@ -14683,13 +14683,13 @@
         <v>0.0</v>
       </c>
       <c r="U205" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V205" t="n">
         <v>0.0</v>
       </c>
       <c r="W205" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="206">
@@ -14721,7 +14721,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" t="n">
-        <v>791.0</v>
+        <v>792.0</v>
       </c>
       <c r="K206" t="n">
         <v>1.0</v>
@@ -14733,10 +14733,10 @@
         <v>0.0</v>
       </c>
       <c r="N206" t="n">
-        <v>791.0</v>
+        <v>792.0</v>
       </c>
       <c r="O206" t="n">
-        <v>507.0</v>
+        <v>508.0</v>
       </c>
       <c r="P206" t="n">
         <v>284.0</v>
@@ -15147,7 +15147,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" t="n">
-        <v>905.0</v>
+        <v>921.0</v>
       </c>
       <c r="K212" t="n">
         <v>1.0</v>
@@ -15159,34 +15159,34 @@
         <v>1.0</v>
       </c>
       <c r="N212" t="n">
-        <v>904.0</v>
+        <v>920.0</v>
       </c>
       <c r="O212" t="n">
-        <v>283.0</v>
+        <v>296.0</v>
       </c>
       <c r="P212" t="n">
-        <v>402.0</v>
+        <v>405.0</v>
       </c>
       <c r="Q212" t="n">
         <v>220.0</v>
       </c>
       <c r="R212" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="S212" t="n">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="T212" t="n">
         <v>0.0</v>
       </c>
       <c r="U212" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="V212" t="n">
         <v>0.0</v>
       </c>
       <c r="W212" t="n">
-        <v>129.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="213">
@@ -15289,7 +15289,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" t="n">
-        <v>808.0</v>
+        <v>818.0</v>
       </c>
       <c r="K214" t="n">
         <v>1.0</v>
@@ -15301,34 +15301,34 @@
         <v>0.0</v>
       </c>
       <c r="N214" t="n">
-        <v>808.0</v>
+        <v>818.0</v>
       </c>
       <c r="O214" t="n">
-        <v>426.0</v>
+        <v>433.0</v>
       </c>
       <c r="P214" t="n">
-        <v>382.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q214" t="n">
         <v>0.0</v>
       </c>
       <c r="R214" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="S214" t="n">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="T214" t="n">
         <v>0.0</v>
       </c>
       <c r="U214" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="V214" t="n">
         <v>3.0</v>
       </c>
       <c r="W214" t="n">
-        <v>113.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="215">
@@ -15644,7 +15644,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" t="n">
-        <v>1065.0</v>
+        <v>1107.0</v>
       </c>
       <c r="K219" t="n">
         <v>1.0</v>
@@ -15656,22 +15656,22 @@
         <v>0.0</v>
       </c>
       <c r="N219" t="n">
-        <v>1065.0</v>
+        <v>1107.0</v>
       </c>
       <c r="O219" t="n">
-        <v>227.0</v>
+        <v>249.0</v>
       </c>
       <c r="P219" t="n">
-        <v>457.0</v>
+        <v>477.0</v>
       </c>
       <c r="Q219" t="n">
         <v>381.0</v>
       </c>
       <c r="R219" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="S219" t="n">
-        <v>53.0</v>
+        <v>60.0</v>
       </c>
       <c r="T219" t="n">
         <v>3.0</v>
@@ -15683,7 +15683,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" t="n">
-        <v>83.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="220">
@@ -15857,7 +15857,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" t="n">
-        <v>916.0</v>
+        <v>950.0</v>
       </c>
       <c r="K222" t="n">
         <v>1.0</v>
@@ -15869,13 +15869,13 @@
         <v>0.0</v>
       </c>
       <c r="N222" t="n">
-        <v>916.0</v>
+        <v>950.0</v>
       </c>
       <c r="O222" t="n">
-        <v>266.0</v>
+        <v>285.0</v>
       </c>
       <c r="P222" t="n">
-        <v>399.0</v>
+        <v>414.0</v>
       </c>
       <c r="Q222" t="n">
         <v>251.0</v>
@@ -16283,7 +16283,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" t="n">
-        <v>1012.0</v>
+        <v>1024.0</v>
       </c>
       <c r="K228" t="n">
         <v>1.0</v>
@@ -16295,10 +16295,10 @@
         <v>0.0</v>
       </c>
       <c r="N228" t="n">
-        <v>1012.0</v>
+        <v>1024.0</v>
       </c>
       <c r="O228" t="n">
-        <v>274.0</v>
+        <v>286.0</v>
       </c>
       <c r="P228" t="n">
         <v>405.0</v>
@@ -16567,7 +16567,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" t="n">
-        <v>982.0</v>
+        <v>1005.0</v>
       </c>
       <c r="K232" t="n">
         <v>1.0</v>
@@ -16579,13 +16579,13 @@
         <v>0.0</v>
       </c>
       <c r="N232" t="n">
-        <v>982.0</v>
+        <v>1005.0</v>
       </c>
       <c r="O232" t="n">
-        <v>130.0</v>
+        <v>147.0</v>
       </c>
       <c r="P232" t="n">
-        <v>204.0</v>
+        <v>210.0</v>
       </c>
       <c r="Q232" t="n">
         <v>648.0</v>
@@ -16594,7 +16594,7 @@
         <v>31.0</v>
       </c>
       <c r="S232" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="T232" t="n">
         <v>0.0</v>
@@ -16606,7 +16606,7 @@
         <v>0.0</v>
       </c>
       <c r="W232" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="233">
@@ -16662,10 +16662,10 @@
         <v>147.0</v>
       </c>
       <c r="R233" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="S233" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="T233" t="n">
         <v>1.0</v>
@@ -16677,7 +16677,7 @@
         <v>0.0</v>
       </c>
       <c r="W233" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
     </row>
   </sheetData>
